--- a/Unity/Assets/Config/Excel/ParticleEffectConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ParticleEffectConfig.xlsx
@@ -81,6 +81,216 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>存在总时长</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否跟随Unit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始位置x</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始位置y</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始位置z</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>缩放x</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>缩放y</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>缩放z</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>otalTime</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>nt</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sFollowUnit</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>osX</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Pos</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Pos</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>caleX</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Scale</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Scale</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>f</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>loat</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"0.1"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"0.5"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>c</t>
     </r>
@@ -94,216 +304,6 @@
       </rPr>
       <t>fx_hit_cwhite</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>存在总时长</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否跟随Unit</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>初始位置x</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>初始位置y</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>初始位置z</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>缩放x</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>缩放y</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>缩放z</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>T</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>otalTime</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>i</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>nt</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>I</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>sFollowUnit</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>osX</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Pos</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Pos</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>caleX</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Scale</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Scale</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>f</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>loat</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>"0.1"</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>"0.5"</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -323,6 +323,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -330,11 +331,13 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -454,7 +457,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -489,7 +492,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -720,28 +723,28 @@
         <v>2</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4" spans="3:12" x14ac:dyDescent="0.3">
@@ -752,28 +755,28 @@
         <v>3</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="J4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="K4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="L4" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="3:12" x14ac:dyDescent="0.3">
@@ -784,35 +787,35 @@
         <v>4</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="3:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E6" s="1">
@@ -825,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
@@ -844,8 +847,8 @@
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>6</v>
+      <c r="D7" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="E7" s="1">
         <v>500</v>
@@ -857,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
